--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2B0DB6-4C64-4316-956C-EA08EBEFE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="6408" yWindow="3456" windowWidth="13836" windowHeight="7116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -83,13 +89,22 @@
   </si>
   <si>
     <t>Custo</t>
+  </si>
+  <si>
+    <t>Locator_AranhaFerreira</t>
+  </si>
+  <si>
+    <t>::</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,24 +156,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +223,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,6 +257,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,9 +292,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -439,11 +468,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,6 +541,1221 @@
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>69</v>
+      </c>
+      <c r="D2">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0.3846</v>
+      </c>
+      <c r="R2" s="5">
+        <v>1</v>
+      </c>
+      <c r="S2" s="5">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>69</v>
+      </c>
+      <c r="D3">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>14</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>69</v>
+      </c>
+      <c r="D4">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>69</v>
+      </c>
+      <c r="D5">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>69</v>
+      </c>
+      <c r="D6">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.52939999999999998</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>69</v>
+      </c>
+      <c r="D7">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>93</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P7" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1075</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B8">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>69</v>
+      </c>
+      <c r="D8">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>69</v>
+      </c>
+      <c r="D9">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" t="s">
+        <v>25</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>69</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" t="s">
+        <v>25</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>25</v>
+      </c>
+      <c r="V10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>69</v>
+      </c>
+      <c r="D11">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" t="s">
+        <v>25</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>25</v>
+      </c>
+      <c r="V11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>69</v>
+      </c>
+      <c r="D12">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>3624</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" t="s">
+        <v>25</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>25</v>
+      </c>
+      <c r="V12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>69</v>
+      </c>
+      <c r="D13">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>3624</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>25</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>25</v>
+      </c>
+      <c r="V13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>69</v>
+      </c>
+      <c r="D14">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>3624</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14" t="s">
+        <v>25</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>25</v>
+      </c>
+      <c r="V14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>69</v>
+      </c>
+      <c r="D15">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>3624</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15" t="s">
+        <v>25</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="s">
+        <v>25</v>
+      </c>
+      <c r="V15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B16">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>69</v>
+      </c>
+      <c r="D16">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>3624</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <v>1937</v>
+      </c>
+      <c r="J16">
+        <v>34</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>4</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="P16" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0.1176</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B17">
+        <v>18</v>
+      </c>
+      <c r="C17">
+        <v>69</v>
+      </c>
+      <c r="D17">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>3624</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>2943</v>
+      </c>
+      <c r="J17">
+        <v>65</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P17" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="R17" s="4">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B18">
+        <v>19</v>
+      </c>
+      <c r="C18">
+        <v>69</v>
+      </c>
+      <c r="D18">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18">
+        <v>3624</v>
+      </c>
+      <c r="G18">
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>3016</v>
+      </c>
+      <c r="J18">
+        <v>73</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>5</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="R18" s="4">
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>69</v>
+      </c>
+      <c r="D19">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>3624</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>32</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19" t="s">
+        <v>25</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" t="s">
+        <v>25</v>
+      </c>
+      <c r="V19" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2B0DB6-4C64-4316-956C-EA08EBEFE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBC8324-842D-437C-B0FF-124565E4BBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6408" yWindow="3456" windowWidth="13836" windowHeight="7116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,8 +469,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1755,6 +1758,278 @@
         <v>25</v>
       </c>
       <c r="V19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>69</v>
+      </c>
+      <c r="D20">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20">
+        <v>1676</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>2921</v>
+      </c>
+      <c r="J20">
+        <v>62</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>2.12E-2</v>
+      </c>
+      <c r="R20" s="4">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>69</v>
+      </c>
+      <c r="D21">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>1676</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>3678</v>
+      </c>
+      <c r="J21">
+        <v>84</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="R21" s="4">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>69</v>
+      </c>
+      <c r="D22">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>1676</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>9899</v>
+      </c>
+      <c r="J22">
+        <v>241</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>2.5462962962962965E-3</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="R22" s="4">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <v>69</v>
+      </c>
+      <c r="D23">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23">
+        <v>1676</v>
+      </c>
+      <c r="G23">
+        <v>7</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>8895</v>
+      </c>
+      <c r="J23">
+        <v>200</v>
+      </c>
+      <c r="K23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>7</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="P23" s="3">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4">
         <v>1</v>
       </c>
     </row>

--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBC8324-842D-437C-B0FF-124565E4BBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0293760-747E-470B-8681-CFA92367D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1988,22 +1988,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>8895</v>
+        <v>9800</v>
       </c>
       <c r="J23">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="K23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2012,25 +2012,569 @@
         <v>4.9768518518518521E-4</v>
       </c>
       <c r="P23" s="3">
-        <v>8.9120370370370373E-4</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="Q23" s="4">
-        <v>2.2499999999999999E-2</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="R23" s="5">
-        <v>0.04</v>
+        <v>4.07E-2</v>
       </c>
       <c r="S23" s="4">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B24">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>69</v>
+      </c>
+      <c r="D24">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24">
+        <v>1676</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>10106</v>
+      </c>
+      <c r="J24">
+        <v>153</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>3</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="P24" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="R24" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="S24" s="5">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B25">
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <v>69</v>
+      </c>
+      <c r="D25">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25">
+        <v>1676</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>10103</v>
+      </c>
+      <c r="J25">
+        <v>164</v>
+      </c>
+      <c r="K25">
+        <v>6</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>6</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P25" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="R25" s="4">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="S25" s="5">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B26">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>69</v>
+      </c>
+      <c r="D26">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26">
+        <v>1676</v>
+      </c>
+      <c r="G26">
+        <v>7</v>
+      </c>
+      <c r="H26">
+        <v>11</v>
+      </c>
+      <c r="I26">
+        <v>3295</v>
+      </c>
+      <c r="J26">
+        <v>142</v>
+      </c>
+      <c r="K26">
+        <v>13</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>13</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P26" s="3">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="R26" s="4">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="S26" s="5">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>69</v>
+      </c>
+      <c r="D27">
+        <v>71</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>1676</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>1497</v>
+      </c>
+      <c r="J27">
+        <v>59</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>3</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P27" s="3">
+        <v>7.9861111111111116E-4</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="R27" s="4">
+        <v>5.0799999999999998E-2</v>
+      </c>
+      <c r="S27" s="5">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27" s="5">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B28">
+        <v>16</v>
+      </c>
+      <c r="C28">
+        <v>69</v>
+      </c>
+      <c r="D28">
+        <v>71</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28">
+        <v>1676</v>
+      </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>1419</v>
+      </c>
+      <c r="J28">
+        <v>42</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>4</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P28" s="3">
+        <v>1.1689814814814816E-3</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="R28" s="4">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="S28" s="5">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" s="5">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B29">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <v>69</v>
+      </c>
+      <c r="D29">
+        <v>71</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29">
+        <v>1676</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P29" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="R29" s="5">
+        <v>0</v>
+      </c>
+      <c r="S29" t="s">
+        <v>25</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>25</v>
+      </c>
+      <c r="V29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B30">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <v>69</v>
+      </c>
+      <c r="D30">
+        <v>71</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30">
+        <v>1676</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1433</v>
+      </c>
+      <c r="J30">
+        <v>35</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30">
+        <v>4</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P30" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="R30" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="S30" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B31">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>69</v>
+      </c>
+      <c r="D31">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31">
+        <v>1676</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>8</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P31" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="4">
         <v>0.125</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23" s="5">
-        <v>0</v>
-      </c>
-      <c r="V23" s="4">
-        <v>1</v>
+      <c r="R31" s="5">
+        <v>1</v>
+      </c>
+      <c r="S31" s="5">
+        <v>1</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>25</v>
+      </c>
+      <c r="V31" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0293760-747E-470B-8681-CFA92367D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C08E90-79CF-4FC0-AF89-AE72F7259AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2580,4 +2581,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299395E7-E414-4FEB-85C5-ABADBD7BB9AB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C08E90-79CF-4FC0-AF89-AE72F7259AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A605D911-5204-4928-8B11-D1AE345A75FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2590,4 +2591,13 @@
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13697C14-C2D4-4C86-8372-B8EEE4A8C2BD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A605D911-5204-4928-8B11-D1AE345A75FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13D3226-D03D-479E-9802-3183069DA1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -946,6 +946,9 @@
       <c r="V7" s="4">
         <v>1</v>
       </c>
+      <c r="W7">
+        <v>9.7500000000000003E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -2466,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30">
         <v>1433</v>
@@ -2478,10 +2481,10 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -2490,7 +2493,7 @@
         <v>4.6296296296296298E-4</v>
       </c>
       <c r="P30" s="3">
-        <v>5.7870370370370373E-5</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="Q30" s="4">
         <v>2.4400000000000002E-2</v>
@@ -2499,7 +2502,7 @@
         <v>0.1429</v>
       </c>
       <c r="S30" s="5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -2531,52 +2534,3074 @@
         <v>1676</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
+        <v>9</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P31" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="R31" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S31" s="5">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31" s="5">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B32">
         <v>8</v>
       </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" s="3">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="C32">
+        <v>69</v>
+      </c>
+      <c r="D32">
+        <v>71</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32">
+        <v>1764</v>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>14</v>
+      </c>
+      <c r="I32">
+        <v>3390</v>
+      </c>
+      <c r="J32">
+        <v>137</v>
+      </c>
+      <c r="K32">
+        <v>20</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>20</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="R32" s="4">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="S32" s="5">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>69</v>
+      </c>
+      <c r="D33">
+        <v>71</v>
+      </c>
+      <c r="E33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33">
+        <v>1764</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>615</v>
+      </c>
+      <c r="J33">
+        <v>33</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P33" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="R33" s="4">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="S33" s="5">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33" s="5">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B34">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>69</v>
+      </c>
+      <c r="D34">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34">
+        <v>1764</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34">
+        <v>1215</v>
+      </c>
+      <c r="J34">
+        <v>34</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>5</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P34" s="3">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R34" s="4">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="S34" s="5">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B35">
+        <v>11</v>
+      </c>
+      <c r="C35">
+        <v>69</v>
+      </c>
+      <c r="D35">
+        <v>71</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35">
+        <v>1764</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>11</v>
+      </c>
+      <c r="I35">
+        <v>5195</v>
+      </c>
+      <c r="J35">
+        <v>176</v>
+      </c>
+      <c r="K35">
+        <v>14</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>14</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="P35" s="3">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>3.39E-2</v>
+      </c>
+      <c r="R35" s="4">
+        <v>7.9500000000000001E-2</v>
+      </c>
+      <c r="S35" s="5">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35" s="5">
+        <v>0</v>
+      </c>
+      <c r="V35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B36">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>69</v>
+      </c>
+      <c r="D36">
+        <v>71</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36">
+        <v>1764</v>
+      </c>
+      <c r="G36">
+        <v>7</v>
+      </c>
+      <c r="H36">
+        <v>6</v>
+      </c>
+      <c r="I36">
+        <v>3338</v>
+      </c>
+      <c r="J36">
+        <v>85</v>
+      </c>
+      <c r="K36">
+        <v>7</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>7</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P36" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="R36" s="4">
+        <v>8.2400000000000001E-2</v>
+      </c>
+      <c r="S36" s="5">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5">
+        <v>0</v>
+      </c>
+      <c r="V36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B37">
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>69</v>
+      </c>
+      <c r="D37">
+        <v>71</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37">
+        <v>1764</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>11</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P37" t="s">
         <v>24</v>
       </c>
-      <c r="Q31" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="R31" s="5">
-        <v>1</v>
-      </c>
-      <c r="S31" s="5">
-        <v>1</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V31" t="s">
-        <v>25</v>
+      <c r="Q37" s="4">
+        <v>0.36359999999999998</v>
+      </c>
+      <c r="R37" s="5">
+        <v>0</v>
+      </c>
+      <c r="S37" t="s">
+        <v>25</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37" t="s">
+        <v>25</v>
+      </c>
+      <c r="V37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B38">
+        <v>14</v>
+      </c>
+      <c r="C38">
+        <v>69</v>
+      </c>
+      <c r="D38">
+        <v>71</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38">
+        <v>1764</v>
+      </c>
+      <c r="G38">
+        <v>7</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>3101</v>
+      </c>
+      <c r="J38">
+        <v>68</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>4</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="P38" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="R38" s="4">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="S38" s="5">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5">
+        <v>0</v>
+      </c>
+      <c r="V38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>69</v>
+      </c>
+      <c r="D39">
+        <v>71</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39">
+        <v>1764</v>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>2902</v>
+      </c>
+      <c r="J39">
+        <v>59</v>
+      </c>
+      <c r="K39">
+        <v>3</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="P39" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="R39" s="4">
+        <v>5.0799999999999998E-2</v>
+      </c>
+      <c r="S39" s="5">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5">
+        <v>0</v>
+      </c>
+      <c r="V39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B40">
+        <v>16</v>
+      </c>
+      <c r="C40">
+        <v>69</v>
+      </c>
+      <c r="D40">
+        <v>71</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40">
+        <v>1764</v>
+      </c>
+      <c r="G40">
+        <v>7</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>1428</v>
+      </c>
+      <c r="J40">
+        <v>30</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="P40" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="R40" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="S40" s="5">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5">
+        <v>0</v>
+      </c>
+      <c r="V40" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B41">
+        <v>17</v>
+      </c>
+      <c r="C41">
+        <v>69</v>
+      </c>
+      <c r="D41">
+        <v>71</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41">
+        <v>1764</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>12</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P41" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="R41" s="5">
+        <v>0</v>
+      </c>
+      <c r="S41" t="s">
+        <v>25</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41" t="s">
+        <v>25</v>
+      </c>
+      <c r="V41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B42">
+        <v>18</v>
+      </c>
+      <c r="C42">
+        <v>69</v>
+      </c>
+      <c r="D42">
+        <v>71</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42">
+        <v>1764</v>
+      </c>
+      <c r="G42">
+        <v>7</v>
+      </c>
+      <c r="H42">
+        <v>3</v>
+      </c>
+      <c r="I42">
+        <v>1406</v>
+      </c>
+      <c r="J42">
+        <v>36</v>
+      </c>
+      <c r="K42">
+        <v>3</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>3</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P42" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="R42" s="4">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="S42" s="5">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" s="5">
+        <v>0</v>
+      </c>
+      <c r="V42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B43">
+        <v>19</v>
+      </c>
+      <c r="C43">
+        <v>69</v>
+      </c>
+      <c r="D43">
+        <v>71</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43">
+        <v>1764</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>15</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="P43" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="R43" s="5">
+        <v>0</v>
+      </c>
+      <c r="S43" t="s">
+        <v>25</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43" t="s">
+        <v>25</v>
+      </c>
+      <c r="V43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>69</v>
+      </c>
+      <c r="D44">
+        <v>71</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44">
+        <v>1413</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>3060</v>
+      </c>
+      <c r="J44">
+        <v>103</v>
+      </c>
+      <c r="K44">
+        <v>14</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>13</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="P44" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="R44" s="4">
+        <v>0.13589999999999999</v>
+      </c>
+      <c r="S44" s="4">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5">
+        <v>0</v>
+      </c>
+      <c r="V44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>69</v>
+      </c>
+      <c r="D45">
+        <v>71</v>
+      </c>
+      <c r="E45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45">
+        <v>1413</v>
+      </c>
+      <c r="G45">
+        <v>7</v>
+      </c>
+      <c r="H45">
+        <v>10</v>
+      </c>
+      <c r="I45">
+        <v>2116</v>
+      </c>
+      <c r="J45">
+        <v>97</v>
+      </c>
+      <c r="K45">
+        <v>10</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>10</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P45" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>4.58E-2</v>
+      </c>
+      <c r="R45" s="4">
+        <v>0.1031</v>
+      </c>
+      <c r="S45" s="5">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45" s="5">
+        <v>0</v>
+      </c>
+      <c r="V45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B46">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>69</v>
+      </c>
+      <c r="D46">
+        <v>71</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46">
+        <v>1413</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>9</v>
+      </c>
+      <c r="I46">
+        <v>2963</v>
+      </c>
+      <c r="J46">
+        <v>120</v>
+      </c>
+      <c r="K46">
+        <v>10</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>10</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P46" s="3">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="R46" s="4">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="S46" s="5">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5">
+        <v>0</v>
+      </c>
+      <c r="V46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B47">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <v>69</v>
+      </c>
+      <c r="D47">
+        <v>71</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47">
+        <v>1413</v>
+      </c>
+      <c r="G47">
+        <v>7</v>
+      </c>
+      <c r="H47">
+        <v>6</v>
+      </c>
+      <c r="I47">
+        <v>3931</v>
+      </c>
+      <c r="J47">
+        <v>110</v>
+      </c>
+      <c r="K47">
+        <v>8</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>8</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P47" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R47" s="4">
+        <v>7.2700000000000001E-2</v>
+      </c>
+      <c r="S47" s="5">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47" s="5">
+        <v>0</v>
+      </c>
+      <c r="V47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B48">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>69</v>
+      </c>
+      <c r="D48">
+        <v>71</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48">
+        <v>1413</v>
+      </c>
+      <c r="G48">
+        <v>7</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>3387</v>
+      </c>
+      <c r="J48">
+        <v>54</v>
+      </c>
+      <c r="K48">
+        <v>3</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P48" s="3">
+        <v>2.0949074074074073E-3</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="R48" s="4">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="S48" s="5">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5">
+        <v>0</v>
+      </c>
+      <c r="V48" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B49">
+        <v>13</v>
+      </c>
+      <c r="C49">
+        <v>69</v>
+      </c>
+      <c r="D49">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49">
+        <v>1413</v>
+      </c>
+      <c r="G49">
+        <v>7</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>2301</v>
+      </c>
+      <c r="J49">
+        <v>43</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="P49" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="R49" s="5">
+        <v>0</v>
+      </c>
+      <c r="S49" t="s">
+        <v>25</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49" t="s">
+        <v>25</v>
+      </c>
+      <c r="V49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B50">
+        <v>14</v>
+      </c>
+      <c r="C50">
+        <v>69</v>
+      </c>
+      <c r="D50">
+        <v>71</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50">
+        <v>1413</v>
+      </c>
+      <c r="G50">
+        <v>7</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1142</v>
+      </c>
+      <c r="J50">
+        <v>27</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P50" s="3">
+        <v>2.3564814814814816E-2</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="R50" s="4">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S50" s="5">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B51">
+        <v>15</v>
+      </c>
+      <c r="C51">
+        <v>69</v>
+      </c>
+      <c r="D51">
+        <v>71</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51">
+        <v>1413</v>
+      </c>
+      <c r="G51">
+        <v>7</v>
+      </c>
+      <c r="H51">
+        <v>5</v>
+      </c>
+      <c r="I51">
+        <v>7034</v>
+      </c>
+      <c r="J51">
+        <v>83</v>
+      </c>
+      <c r="K51">
+        <v>5</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>5</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="P51" s="3">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>1.18E-2</v>
+      </c>
+      <c r="R51" s="4">
+        <v>6.0199999999999997E-2</v>
+      </c>
+      <c r="S51" s="5">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51" s="5">
+        <v>0</v>
+      </c>
+      <c r="V51" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B52">
+        <v>16</v>
+      </c>
+      <c r="C52">
+        <v>69</v>
+      </c>
+      <c r="D52">
+        <v>71</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52">
+        <v>1413</v>
+      </c>
+      <c r="G52">
+        <v>7</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <v>5386</v>
+      </c>
+      <c r="J52">
+        <v>70</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>5</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R52" s="4">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="S52" s="5">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>69</v>
+      </c>
+      <c r="D53">
+        <v>71</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53">
+        <v>1599</v>
+      </c>
+      <c r="G53">
+        <v>7</v>
+      </c>
+      <c r="H53">
+        <v>14</v>
+      </c>
+      <c r="I53">
+        <v>5347</v>
+      </c>
+      <c r="J53">
+        <v>135</v>
+      </c>
+      <c r="K53">
+        <v>15</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>15</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P53" s="3">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>2.52E-2</v>
+      </c>
+      <c r="R53" s="4">
+        <v>0.1111</v>
+      </c>
+      <c r="S53" s="5">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53" s="5">
+        <v>0</v>
+      </c>
+      <c r="V53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54">
+        <v>69</v>
+      </c>
+      <c r="D54">
+        <v>71</v>
+      </c>
+      <c r="E54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54">
+        <v>1599</v>
+      </c>
+      <c r="G54">
+        <v>7</v>
+      </c>
+      <c r="H54">
+        <v>9</v>
+      </c>
+      <c r="I54">
+        <v>6726</v>
+      </c>
+      <c r="J54">
+        <v>129</v>
+      </c>
+      <c r="K54">
+        <v>12</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>12</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P54" s="3">
+        <v>1.2731481481481483E-3</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="R54" s="4">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="S54" s="5">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5">
+        <v>0</v>
+      </c>
+      <c r="V54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B55">
+        <v>10</v>
+      </c>
+      <c r="C55">
+        <v>69</v>
+      </c>
+      <c r="D55">
+        <v>71</v>
+      </c>
+      <c r="E55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55">
+        <v>1599</v>
+      </c>
+      <c r="G55">
+        <v>7</v>
+      </c>
+      <c r="H55">
+        <v>5</v>
+      </c>
+      <c r="I55">
+        <v>7505</v>
+      </c>
+      <c r="J55">
+        <v>141</v>
+      </c>
+      <c r="K55">
+        <v>5</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>5</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P55" s="3">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="R55" s="4">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="S55" s="5">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" s="5">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B56">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>69</v>
+      </c>
+      <c r="D56">
+        <v>71</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56">
+        <v>1599</v>
+      </c>
+      <c r="G56">
+        <v>7</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
+      </c>
+      <c r="I56">
+        <v>7130</v>
+      </c>
+      <c r="J56">
+        <v>128</v>
+      </c>
+      <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>2</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="P56" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="R56" s="4">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="S56" s="5">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56" s="5">
+        <v>0</v>
+      </c>
+      <c r="V56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57">
+        <v>69</v>
+      </c>
+      <c r="D57">
+        <v>71</v>
+      </c>
+      <c r="E57" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57">
+        <v>1599</v>
+      </c>
+      <c r="G57">
+        <v>7</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
+      </c>
+      <c r="I57">
+        <v>5048</v>
+      </c>
+      <c r="J57">
+        <v>59</v>
+      </c>
+      <c r="K57">
+        <v>4</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>4</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="P57" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="Q57" s="4">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R57" s="4">
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="S57" s="5">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57" s="5">
+        <v>0</v>
+      </c>
+      <c r="V57" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B58">
+        <v>13</v>
+      </c>
+      <c r="C58">
+        <v>69</v>
+      </c>
+      <c r="D58">
+        <v>71</v>
+      </c>
+      <c r="E58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58">
+        <v>1599</v>
+      </c>
+      <c r="G58">
+        <v>7</v>
+      </c>
+      <c r="H58">
+        <v>8</v>
+      </c>
+      <c r="I58">
+        <v>4361</v>
+      </c>
+      <c r="J58">
+        <v>153</v>
+      </c>
+      <c r="K58">
+        <v>11</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>10</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="P58" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="Q58" s="4">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="R58" s="4">
+        <v>7.1900000000000006E-2</v>
+      </c>
+      <c r="S58" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5">
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B59">
+        <v>14</v>
+      </c>
+      <c r="C59">
+        <v>69</v>
+      </c>
+      <c r="D59">
+        <v>71</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59">
+        <v>1599</v>
+      </c>
+      <c r="G59">
+        <v>7</v>
+      </c>
+      <c r="H59">
+        <v>5</v>
+      </c>
+      <c r="I59">
+        <v>6692</v>
+      </c>
+      <c r="J59">
+        <v>134</v>
+      </c>
+      <c r="K59">
+        <v>5</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>5</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="P59" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="R59" s="4">
+        <v>3.73E-2</v>
+      </c>
+      <c r="S59" s="5">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59" s="5">
+        <v>0</v>
+      </c>
+      <c r="V59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
+      <c r="C60">
+        <v>69</v>
+      </c>
+      <c r="D60">
+        <v>71</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60">
+        <v>1599</v>
+      </c>
+      <c r="G60">
+        <v>7</v>
+      </c>
+      <c r="H60">
+        <v>6</v>
+      </c>
+      <c r="I60">
+        <v>4868</v>
+      </c>
+      <c r="J60">
+        <v>79</v>
+      </c>
+      <c r="K60">
+        <v>7</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>6</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="P60" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="R60" s="4">
+        <v>8.8599999999999998E-2</v>
+      </c>
+      <c r="S60" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B61">
+        <v>16</v>
+      </c>
+      <c r="C61">
+        <v>69</v>
+      </c>
+      <c r="D61">
+        <v>71</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61">
+        <v>1599</v>
+      </c>
+      <c r="G61">
+        <v>7</v>
+      </c>
+      <c r="H61">
+        <v>4</v>
+      </c>
+      <c r="I61">
+        <v>5821</v>
+      </c>
+      <c r="J61">
+        <v>97</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P61" s="3">
+        <v>1.8171296296296297E-3</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>1.67E-2</v>
+      </c>
+      <c r="R61" s="4">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="S61" s="5">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61" s="5">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B62">
+        <v>17</v>
+      </c>
+      <c r="C62">
+        <v>69</v>
+      </c>
+      <c r="D62">
+        <v>71</v>
+      </c>
+      <c r="E62" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62">
+        <v>1599</v>
+      </c>
+      <c r="G62">
+        <v>7</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>4340</v>
+      </c>
+      <c r="J62">
+        <v>43</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>1.1574074074074073E-3</v>
+      </c>
+      <c r="P62" s="3">
+        <v>1.8865740740740742E-3</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="R62" s="4">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="S62" s="5">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B63">
+        <v>18</v>
+      </c>
+      <c r="C63">
+        <v>69</v>
+      </c>
+      <c r="D63">
+        <v>71</v>
+      </c>
+      <c r="E63" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63">
+        <v>1599</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>12</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P63" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="R63" s="5">
+        <v>0</v>
+      </c>
+      <c r="S63" t="s">
+        <v>25</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63" t="s">
+        <v>25</v>
+      </c>
+      <c r="V63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B64">
+        <v>19</v>
+      </c>
+      <c r="C64">
+        <v>69</v>
+      </c>
+      <c r="D64">
+        <v>71</v>
+      </c>
+      <c r="E64" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64">
+        <v>1599</v>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>909</v>
+      </c>
+      <c r="J64">
+        <v>25</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P64" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>2.75E-2</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="S64" s="5">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5">
+        <v>0</v>
+      </c>
+      <c r="V64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>69</v>
+      </c>
+      <c r="D65">
+        <v>71</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65">
+        <v>1923</v>
+      </c>
+      <c r="G65">
+        <v>7</v>
+      </c>
+      <c r="H65">
+        <v>12</v>
+      </c>
+      <c r="I65">
+        <v>4445</v>
+      </c>
+      <c r="J65">
+        <v>191</v>
+      </c>
+      <c r="K65">
+        <v>16</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>16</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P65" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R65" s="4">
+        <v>8.3799999999999999E-2</v>
+      </c>
+      <c r="S65" s="5">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" s="5">
+        <v>0</v>
+      </c>
+      <c r="V65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B66">
+        <v>9</v>
+      </c>
+      <c r="C66">
+        <v>69</v>
+      </c>
+      <c r="D66">
+        <v>71</v>
+      </c>
+      <c r="E66" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66">
+        <v>1923</v>
+      </c>
+      <c r="G66">
+        <v>7</v>
+      </c>
+      <c r="H66">
+        <v>15</v>
+      </c>
+      <c r="I66">
+        <v>5658</v>
+      </c>
+      <c r="J66">
+        <v>174</v>
+      </c>
+      <c r="K66">
+        <v>23</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>23</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P66" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="R66" s="4">
+        <v>0.13220000000000001</v>
+      </c>
+      <c r="S66" s="5">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5">
+        <v>0</v>
+      </c>
+      <c r="V66" s="4">
+        <v>1</v>
+      </c>
+      <c r="W66">
+        <v>28.5045</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67">
+        <v>69</v>
+      </c>
+      <c r="D67">
+        <v>71</v>
+      </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67">
+        <v>1923</v>
+      </c>
+      <c r="G67">
+        <v>7</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>6700</v>
+      </c>
+      <c r="J67">
+        <v>115</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>5</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P67" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>1.72E-2</v>
+      </c>
+      <c r="R67" s="4">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="S67" s="4">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67" s="5">
+        <v>0</v>
+      </c>
+      <c r="V67" s="4">
+        <v>1</v>
+      </c>
+      <c r="W67">
+        <v>96.706999999999994</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B68">
+        <v>11</v>
+      </c>
+      <c r="C68">
+        <v>69</v>
+      </c>
+      <c r="D68">
+        <v>71</v>
+      </c>
+      <c r="E68" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68">
+        <v>1923</v>
+      </c>
+      <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>6998</v>
+      </c>
+      <c r="J68">
+        <v>128</v>
+      </c>
+      <c r="K68">
+        <v>7</v>
+      </c>
+      <c r="L68">
+        <v>4</v>
+      </c>
+      <c r="M68">
+        <v>3</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="P68" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>1.83E-2</v>
+      </c>
+      <c r="R68" s="4">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="S68" s="4">
+        <v>0.57140000000000002</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5">
+        <v>0</v>
+      </c>
+      <c r="V68" s="4">
+        <v>1</v>
+      </c>
+      <c r="W68">
+        <v>90.899000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>69</v>
+      </c>
+      <c r="D69">
+        <v>71</v>
+      </c>
+      <c r="E69" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69">
+        <v>1923</v>
+      </c>
+      <c r="G69">
+        <v>7</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>1253</v>
+      </c>
+      <c r="J69">
+        <v>15</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>9.2592592592592596E-4</v>
+      </c>
+      <c r="P69" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R69" s="4">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="S69" s="5">
+        <v>1</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69" t="s">
+        <v>25</v>
+      </c>
+      <c r="V69" t="s">
+        <v>25</v>
+      </c>
+      <c r="W69">
+        <v>17.546500000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B70">
+        <v>13</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+      <c r="D70">
+        <v>71</v>
+      </c>
+      <c r="E70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70">
+        <v>1923</v>
+      </c>
+      <c r="G70">
+        <v>7</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>2424</v>
+      </c>
+      <c r="J70">
+        <v>32</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="P70" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>1.32E-2</v>
+      </c>
+      <c r="R70" s="4">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="S70" s="5">
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70" t="s">
+        <v>25</v>
+      </c>
+      <c r="V70" t="s">
+        <v>25</v>
+      </c>
+      <c r="W70">
+        <v>34.383000000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B71">
+        <v>14</v>
+      </c>
+      <c r="C71">
+        <v>69</v>
+      </c>
+      <c r="D71">
+        <v>71</v>
+      </c>
+      <c r="E71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71">
+        <v>1923</v>
+      </c>
+      <c r="G71">
+        <v>7</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>4997</v>
+      </c>
+      <c r="J71">
+        <v>75</v>
+      </c>
+      <c r="K71">
+        <v>4</v>
+      </c>
+      <c r="L71">
+        <v>4</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="P71" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="R71" s="4">
+        <v>5.33E-2</v>
+      </c>
+      <c r="S71" s="5">
+        <v>1</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71" t="s">
+        <v>25</v>
+      </c>
+      <c r="V71" t="s">
+        <v>25</v>
+      </c>
+      <c r="W71">
+        <v>68.096000000000004</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72">
+        <v>69</v>
+      </c>
+      <c r="D72">
+        <v>71</v>
+      </c>
+      <c r="E72" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72">
+        <v>1923</v>
+      </c>
+      <c r="G72">
+        <v>7</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>5097</v>
+      </c>
+      <c r="J72">
+        <v>59</v>
+      </c>
+      <c r="K72">
+        <v>2</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="P72" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="R72" s="4">
+        <v>3.39E-2</v>
+      </c>
+      <c r="S72" s="5">
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72" t="s">
+        <v>25</v>
+      </c>
+      <c r="V72" t="s">
+        <v>25</v>
+      </c>
+      <c r="W72">
+        <v>65.134500000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B73">
+        <v>16</v>
+      </c>
+      <c r="C73">
+        <v>69</v>
+      </c>
+      <c r="D73">
+        <v>71</v>
+      </c>
+      <c r="E73" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73">
+        <v>1923</v>
+      </c>
+      <c r="G73">
+        <v>7</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>1451</v>
+      </c>
+      <c r="J73">
+        <v>17</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="P73" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R73" s="5">
+        <v>0</v>
+      </c>
+      <c r="S73" t="s">
+        <v>25</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73" t="s">
+        <v>25</v>
+      </c>
+      <c r="V73" t="s">
+        <v>25</v>
+      </c>
+      <c r="W73">
+        <v>19.627500000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B74">
+        <v>17</v>
+      </c>
+      <c r="C74">
+        <v>69</v>
+      </c>
+      <c r="D74">
+        <v>71</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74">
+        <v>1923</v>
+      </c>
+      <c r="G74">
+        <v>4</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>467</v>
+      </c>
+      <c r="J74">
+        <v>4</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="P74" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>8.6E-3</v>
+      </c>
+      <c r="R74" s="5">
+        <v>0</v>
+      </c>
+      <c r="S74" t="s">
+        <v>25</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74" t="s">
+        <v>25</v>
+      </c>
+      <c r="V74" t="s">
+        <v>25</v>
+      </c>
+      <c r="W74">
+        <v>5.5635000000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B75">
+        <v>19</v>
+      </c>
+      <c r="C75">
+        <v>69</v>
+      </c>
+      <c r="D75">
+        <v>71</v>
+      </c>
+      <c r="E75" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75">
+        <v>1923</v>
+      </c>
+      <c r="G75">
+        <v>3</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>301</v>
+      </c>
+      <c r="J75">
+        <v>3</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>1.1342592592592593E-3</v>
+      </c>
+      <c r="P75" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="R75" s="5">
+        <v>0</v>
+      </c>
+      <c r="S75" t="s">
+        <v>25</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75" t="s">
+        <v>25</v>
+      </c>
+      <c r="V75" t="s">
+        <v>25</v>
+      </c>
+      <c r="W75">
+        <v>3.7519999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_aranha_ferreira.xlsx
+++ b/data/base_aranha_ferreira.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13D3226-D03D-479E-9802-3183069DA1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F062DD-EE39-46B3-9DCC-35D138505DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -5602,6 +5602,4834 @@
       </c>
       <c r="W75">
         <v>3.7519999999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B76">
+        <v>8</v>
+      </c>
+      <c r="C76">
+        <v>69</v>
+      </c>
+      <c r="D76">
+        <v>71</v>
+      </c>
+      <c r="E76" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76">
+        <v>1089</v>
+      </c>
+      <c r="G76">
+        <v>7</v>
+      </c>
+      <c r="H76">
+        <v>12</v>
+      </c>
+      <c r="I76">
+        <v>1742</v>
+      </c>
+      <c r="J76">
+        <v>86</v>
+      </c>
+      <c r="K76">
+        <v>14</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>14</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P76" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="R76" s="4">
+        <v>0.1628</v>
+      </c>
+      <c r="S76" s="5">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5">
+        <v>0</v>
+      </c>
+      <c r="V76" s="4">
+        <v>1</v>
+      </c>
+      <c r="W76">
+        <v>29.4665</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B77">
+        <v>9</v>
+      </c>
+      <c r="C77">
+        <v>69</v>
+      </c>
+      <c r="D77">
+        <v>71</v>
+      </c>
+      <c r="E77" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77">
+        <v>1089</v>
+      </c>
+      <c r="G77">
+        <v>7</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>1326</v>
+      </c>
+      <c r="J77">
+        <v>67</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P77" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="R77" s="4">
+        <v>1.49E-2</v>
+      </c>
+      <c r="S77" s="5">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77" s="5">
+        <v>0</v>
+      </c>
+      <c r="V77" s="4">
+        <v>1</v>
+      </c>
+      <c r="W77">
+        <v>11.4915</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B78">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>69</v>
+      </c>
+      <c r="D78">
+        <v>71</v>
+      </c>
+      <c r="E78" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78">
+        <v>1089</v>
+      </c>
+      <c r="G78">
+        <v>7</v>
+      </c>
+      <c r="H78">
+        <v>5</v>
+      </c>
+      <c r="I78">
+        <v>2427</v>
+      </c>
+      <c r="J78">
+        <v>62</v>
+      </c>
+      <c r="K78">
+        <v>5</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>5</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="P78" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="R78" s="4">
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="S78" s="5">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5">
+        <v>0</v>
+      </c>
+      <c r="V78" s="4">
+        <v>1</v>
+      </c>
+      <c r="W78">
+        <v>26.226500000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B79">
+        <v>11</v>
+      </c>
+      <c r="C79">
+        <v>69</v>
+      </c>
+      <c r="D79">
+        <v>71</v>
+      </c>
+      <c r="E79" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79">
+        <v>1089</v>
+      </c>
+      <c r="G79">
+        <v>7</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>2005</v>
+      </c>
+      <c r="J79">
+        <v>92</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P79" s="3">
+        <v>2.9976851851851853E-3</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="R79" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="S79" s="5">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79" s="5">
+        <v>0</v>
+      </c>
+      <c r="V79" s="4">
+        <v>1</v>
+      </c>
+      <c r="W79">
+        <v>17.07</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B80">
+        <v>12</v>
+      </c>
+      <c r="C80">
+        <v>69</v>
+      </c>
+      <c r="D80">
+        <v>71</v>
+      </c>
+      <c r="E80" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80">
+        <v>1089</v>
+      </c>
+      <c r="G80">
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <v>3</v>
+      </c>
+      <c r="I80">
+        <v>2970</v>
+      </c>
+      <c r="J80">
+        <v>71</v>
+      </c>
+      <c r="K80">
+        <v>3</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>3</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P80" s="3">
+        <v>2.9398148148148148E-3</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="R80" s="4">
+        <v>4.2299999999999997E-2</v>
+      </c>
+      <c r="S80" s="5">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80" s="5">
+        <v>0</v>
+      </c>
+      <c r="V80" s="4">
+        <v>1</v>
+      </c>
+      <c r="W80">
+        <v>22.712499999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B81">
+        <v>13</v>
+      </c>
+      <c r="C81">
+        <v>69</v>
+      </c>
+      <c r="D81">
+        <v>71</v>
+      </c>
+      <c r="E81" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81">
+        <v>1089</v>
+      </c>
+      <c r="G81">
+        <v>7</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>2081</v>
+      </c>
+      <c r="J81">
+        <v>21</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="P81" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>1.01E-2</v>
+      </c>
+      <c r="R81" s="5">
+        <v>0</v>
+      </c>
+      <c r="S81" t="s">
+        <v>25</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81" t="s">
+        <v>25</v>
+      </c>
+      <c r="V81" s="4">
+        <v>1</v>
+      </c>
+      <c r="W81">
+        <v>6.7309999999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B82">
+        <v>14</v>
+      </c>
+      <c r="C82">
+        <v>69</v>
+      </c>
+      <c r="D82">
+        <v>71</v>
+      </c>
+      <c r="E82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82">
+        <v>1089</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>719</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3">
+        <v>3.8773148148148148E-3</v>
+      </c>
+      <c r="P82" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>2.8E-3</v>
+      </c>
+      <c r="R82" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S82" s="5">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82" s="5">
+        <v>0</v>
+      </c>
+      <c r="V82" s="4">
+        <v>1</v>
+      </c>
+      <c r="W82">
+        <v>1.4495</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B83">
+        <v>15</v>
+      </c>
+      <c r="C83">
+        <v>69</v>
+      </c>
+      <c r="D83">
+        <v>71</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83">
+        <v>1089</v>
+      </c>
+      <c r="G83">
+        <v>7</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>5088</v>
+      </c>
+      <c r="J83">
+        <v>93</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P83" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>1.83E-2</v>
+      </c>
+      <c r="R83" s="4">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="S83" s="5">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83" s="5">
+        <v>0</v>
+      </c>
+      <c r="V83" s="4">
+        <v>1</v>
+      </c>
+      <c r="W83">
+        <v>37.53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>69</v>
+      </c>
+      <c r="D84">
+        <v>71</v>
+      </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84">
+        <v>1089</v>
+      </c>
+      <c r="G84">
+        <v>7</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>3496</v>
+      </c>
+      <c r="J84">
+        <v>83</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P84" s="3">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="R84" s="4">
+        <v>2.41E-2</v>
+      </c>
+      <c r="S84" s="5">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5">
+        <v>0</v>
+      </c>
+      <c r="V84" s="4">
+        <v>1</v>
+      </c>
+      <c r="W84">
+        <v>14.375500000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B85">
+        <v>17</v>
+      </c>
+      <c r="C85">
+        <v>69</v>
+      </c>
+      <c r="D85">
+        <v>71</v>
+      </c>
+      <c r="E85" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85">
+        <v>1089</v>
+      </c>
+      <c r="G85">
+        <v>7</v>
+      </c>
+      <c r="H85">
+        <v>4</v>
+      </c>
+      <c r="I85">
+        <v>3128</v>
+      </c>
+      <c r="J85">
+        <v>62</v>
+      </c>
+      <c r="K85">
+        <v>4</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="P85" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="R85" s="4">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="S85" s="5">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85" s="5">
+        <v>0</v>
+      </c>
+      <c r="V85" s="4">
+        <v>1</v>
+      </c>
+      <c r="W85">
+        <v>6.0685000000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B86">
+        <v>18</v>
+      </c>
+      <c r="C86">
+        <v>69</v>
+      </c>
+      <c r="D86">
+        <v>71</v>
+      </c>
+      <c r="E86" t="s">
+        <v>23</v>
+      </c>
+      <c r="F86">
+        <v>1089</v>
+      </c>
+      <c r="G86">
+        <v>7</v>
+      </c>
+      <c r="H86">
+        <v>3</v>
+      </c>
+      <c r="I86">
+        <v>787</v>
+      </c>
+      <c r="J86">
+        <v>30</v>
+      </c>
+      <c r="K86">
+        <v>3</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="P86" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="R86" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="S86" s="5">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86" s="5">
+        <v>0</v>
+      </c>
+      <c r="V86" s="4">
+        <v>1</v>
+      </c>
+      <c r="W86">
+        <v>21.1465</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B87">
+        <v>19</v>
+      </c>
+      <c r="C87">
+        <v>69</v>
+      </c>
+      <c r="D87">
+        <v>71</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87">
+        <v>1089</v>
+      </c>
+      <c r="G87">
+        <v>7</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>1314</v>
+      </c>
+      <c r="J87">
+        <v>24</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="P87" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>1.83E-2</v>
+      </c>
+      <c r="R87" s="5">
+        <v>0</v>
+      </c>
+      <c r="S87" t="s">
+        <v>25</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87" t="s">
+        <v>25</v>
+      </c>
+      <c r="V87" t="s">
+        <v>25</v>
+      </c>
+      <c r="W87">
+        <v>12.845499999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B88">
+        <v>8</v>
+      </c>
+      <c r="C88">
+        <v>69</v>
+      </c>
+      <c r="D88">
+        <v>71</v>
+      </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88">
+        <v>1618</v>
+      </c>
+      <c r="G88">
+        <v>7</v>
+      </c>
+      <c r="H88">
+        <v>7</v>
+      </c>
+      <c r="I88">
+        <v>5008</v>
+      </c>
+      <c r="J88">
+        <v>131</v>
+      </c>
+      <c r="K88">
+        <v>7</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>7</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="P88" s="3">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="R88" s="4">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="S88" s="5">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88" s="5">
+        <v>0</v>
+      </c>
+      <c r="V88" s="4">
+        <v>1</v>
+      </c>
+      <c r="W88">
+        <v>57.360999999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B89">
+        <v>9</v>
+      </c>
+      <c r="C89">
+        <v>69</v>
+      </c>
+      <c r="D89">
+        <v>71</v>
+      </c>
+      <c r="E89" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89">
+        <v>1618</v>
+      </c>
+      <c r="G89">
+        <v>7</v>
+      </c>
+      <c r="H89">
+        <v>5</v>
+      </c>
+      <c r="I89">
+        <v>6894</v>
+      </c>
+      <c r="J89">
+        <v>222</v>
+      </c>
+      <c r="K89">
+        <v>8</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>8</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="P89" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="R89" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S89" s="5">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89" s="5">
+        <v>0</v>
+      </c>
+      <c r="V89" s="4">
+        <v>1</v>
+      </c>
+      <c r="W89">
+        <v>36.573</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B90">
+        <v>10</v>
+      </c>
+      <c r="C90">
+        <v>69</v>
+      </c>
+      <c r="D90">
+        <v>71</v>
+      </c>
+      <c r="E90" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90">
+        <v>1618</v>
+      </c>
+      <c r="G90">
+        <v>7</v>
+      </c>
+      <c r="H90">
+        <v>4</v>
+      </c>
+      <c r="I90">
+        <v>1688</v>
+      </c>
+      <c r="J90">
+        <v>45</v>
+      </c>
+      <c r="K90">
+        <v>4</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>4</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="P90" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="R90" s="4">
+        <v>8.8900000000000007E-2</v>
+      </c>
+      <c r="S90" s="5">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90" s="5">
+        <v>0</v>
+      </c>
+      <c r="V90" s="4">
+        <v>1</v>
+      </c>
+      <c r="W90">
+        <v>4.8834999999999997</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B91">
+        <v>11</v>
+      </c>
+      <c r="C91">
+        <v>69</v>
+      </c>
+      <c r="D91">
+        <v>71</v>
+      </c>
+      <c r="E91" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91">
+        <v>1618</v>
+      </c>
+      <c r="G91">
+        <v>7</v>
+      </c>
+      <c r="H91">
+        <v>5</v>
+      </c>
+      <c r="I91">
+        <v>3079</v>
+      </c>
+      <c r="J91">
+        <v>85</v>
+      </c>
+      <c r="K91">
+        <v>5</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>5</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P91" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>2.76E-2</v>
+      </c>
+      <c r="R91" s="4">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="S91" s="5">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91" s="5">
+        <v>0</v>
+      </c>
+      <c r="V91" s="4">
+        <v>1</v>
+      </c>
+      <c r="W91">
+        <v>29.9435</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B92">
+        <v>12</v>
+      </c>
+      <c r="C92">
+        <v>69</v>
+      </c>
+      <c r="D92">
+        <v>71</v>
+      </c>
+      <c r="E92" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92">
+        <v>1618</v>
+      </c>
+      <c r="G92">
+        <v>7</v>
+      </c>
+      <c r="H92">
+        <v>6</v>
+      </c>
+      <c r="I92">
+        <v>4040</v>
+      </c>
+      <c r="J92">
+        <v>192</v>
+      </c>
+      <c r="K92">
+        <v>9</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>8</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P92" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="R92" s="4">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="S92" s="4">
+        <v>0.1111</v>
+      </c>
+      <c r="T92">
+        <v>0</v>
+      </c>
+      <c r="U92" s="5">
+        <v>0</v>
+      </c>
+      <c r="V92" s="4">
+        <v>1</v>
+      </c>
+      <c r="W92">
+        <v>45.741500000000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B93">
+        <v>13</v>
+      </c>
+      <c r="C93">
+        <v>69</v>
+      </c>
+      <c r="D93">
+        <v>71</v>
+      </c>
+      <c r="E93" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93">
+        <v>1618</v>
+      </c>
+      <c r="G93">
+        <v>7</v>
+      </c>
+      <c r="H93">
+        <v>4</v>
+      </c>
+      <c r="I93">
+        <v>2636</v>
+      </c>
+      <c r="J93">
+        <v>130</v>
+      </c>
+      <c r="K93">
+        <v>9</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>9</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P93" s="3">
+        <v>2.2453703703703702E-3</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="R93" s="4">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="S93" s="5">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>0</v>
+      </c>
+      <c r="U93" s="5">
+        <v>0</v>
+      </c>
+      <c r="V93" s="4">
+        <v>1</v>
+      </c>
+      <c r="W93">
+        <v>14.622</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B94">
+        <v>14</v>
+      </c>
+      <c r="C94">
+        <v>69</v>
+      </c>
+      <c r="D94">
+        <v>71</v>
+      </c>
+      <c r="E94" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94">
+        <v>1618</v>
+      </c>
+      <c r="G94">
+        <v>7</v>
+      </c>
+      <c r="H94">
+        <v>4</v>
+      </c>
+      <c r="I94">
+        <v>5480</v>
+      </c>
+      <c r="J94">
+        <v>126</v>
+      </c>
+      <c r="K94">
+        <v>5</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>5</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="P94" s="3">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>2.3E-2</v>
+      </c>
+      <c r="R94" s="4">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="S94" s="5">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>0</v>
+      </c>
+      <c r="U94" s="5">
+        <v>0</v>
+      </c>
+      <c r="V94" s="4">
+        <v>1</v>
+      </c>
+      <c r="W94">
+        <v>50.0015</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B95">
+        <v>15</v>
+      </c>
+      <c r="C95">
+        <v>69</v>
+      </c>
+      <c r="D95">
+        <v>71</v>
+      </c>
+      <c r="E95" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95">
+        <v>1618</v>
+      </c>
+      <c r="G95">
+        <v>7</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>1645</v>
+      </c>
+      <c r="J95">
+        <v>36</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P95" s="3">
+        <v>1.7476851851851852E-3</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="R95" s="4">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="S95" s="5">
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <v>0</v>
+      </c>
+      <c r="U95" s="5">
+        <v>0</v>
+      </c>
+      <c r="V95" s="4">
+        <v>1</v>
+      </c>
+      <c r="W95">
+        <v>14.0025</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B96">
+        <v>16</v>
+      </c>
+      <c r="C96">
+        <v>69</v>
+      </c>
+      <c r="D96">
+        <v>71</v>
+      </c>
+      <c r="E96" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96">
+        <v>1618</v>
+      </c>
+      <c r="G96">
+        <v>7</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+      <c r="I96">
+        <v>3529</v>
+      </c>
+      <c r="J96">
+        <v>91</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>3</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="P96" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>2.58E-2</v>
+      </c>
+      <c r="R96" s="4">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="S96" s="5">
+        <v>0</v>
+      </c>
+      <c r="T96">
+        <v>0</v>
+      </c>
+      <c r="U96" s="5">
+        <v>0</v>
+      </c>
+      <c r="V96" s="4">
+        <v>1</v>
+      </c>
+      <c r="W96">
+        <v>16.16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B97">
+        <v>17</v>
+      </c>
+      <c r="C97">
+        <v>69</v>
+      </c>
+      <c r="D97">
+        <v>71</v>
+      </c>
+      <c r="E97" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97">
+        <v>1618</v>
+      </c>
+      <c r="G97">
+        <v>7</v>
+      </c>
+      <c r="H97">
+        <v>5</v>
+      </c>
+      <c r="I97">
+        <v>5281</v>
+      </c>
+      <c r="J97">
+        <v>158</v>
+      </c>
+      <c r="K97">
+        <v>8</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>8</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P97" s="3">
+        <v>1.4004629629629629E-3</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="R97" s="4">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="S97" s="5">
+        <v>0</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97" s="5">
+        <v>0</v>
+      </c>
+      <c r="V97" s="4">
+        <v>1</v>
+      </c>
+      <c r="W97">
+        <v>45.404000000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B98">
+        <v>18</v>
+      </c>
+      <c r="C98">
+        <v>69</v>
+      </c>
+      <c r="D98">
+        <v>71</v>
+      </c>
+      <c r="E98" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98">
+        <v>1618</v>
+      </c>
+      <c r="G98">
+        <v>7</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>359</v>
+      </c>
+      <c r="J98">
+        <v>17</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P98" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="R98" s="4">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="S98" s="5">
+        <v>1</v>
+      </c>
+      <c r="T98">
+        <v>0</v>
+      </c>
+      <c r="U98" t="s">
+        <v>25</v>
+      </c>
+      <c r="V98" s="4">
+        <v>1</v>
+      </c>
+      <c r="W98">
+        <v>8.4280000000000008</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B99">
+        <v>19</v>
+      </c>
+      <c r="C99">
+        <v>69</v>
+      </c>
+      <c r="D99">
+        <v>71</v>
+      </c>
+      <c r="E99" t="s">
+        <v>23</v>
+      </c>
+      <c r="F99">
+        <v>1618</v>
+      </c>
+      <c r="G99">
+        <v>7</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>1313</v>
+      </c>
+      <c r="J99">
+        <v>40</v>
+      </c>
+      <c r="K99">
+        <v>3</v>
+      </c>
+      <c r="L99">
+        <v>3</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P99" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="R99" s="4">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="S99" s="5">
+        <v>1</v>
+      </c>
+      <c r="T99">
+        <v>0</v>
+      </c>
+      <c r="U99" t="s">
+        <v>25</v>
+      </c>
+      <c r="V99" t="s">
+        <v>25</v>
+      </c>
+      <c r="W99">
+        <v>10.542999999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B100">
+        <v>8</v>
+      </c>
+      <c r="C100">
+        <v>69</v>
+      </c>
+      <c r="D100">
+        <v>71</v>
+      </c>
+      <c r="E100" t="s">
+        <v>23</v>
+      </c>
+      <c r="F100">
+        <v>1637</v>
+      </c>
+      <c r="G100">
+        <v>7</v>
+      </c>
+      <c r="H100">
+        <v>6</v>
+      </c>
+      <c r="I100">
+        <v>4238</v>
+      </c>
+      <c r="J100">
+        <v>110</v>
+      </c>
+      <c r="K100">
+        <v>7</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>6</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="P100" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="R100" s="4">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="S100" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="T100">
+        <v>0</v>
+      </c>
+      <c r="U100" s="5">
+        <v>0</v>
+      </c>
+      <c r="V100" s="4">
+        <v>1</v>
+      </c>
+      <c r="W100">
+        <v>46.531999999999996</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B101">
+        <v>9</v>
+      </c>
+      <c r="C101">
+        <v>69</v>
+      </c>
+      <c r="D101">
+        <v>71</v>
+      </c>
+      <c r="E101" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101">
+        <v>1637</v>
+      </c>
+      <c r="G101">
+        <v>7</v>
+      </c>
+      <c r="H101">
+        <v>3</v>
+      </c>
+      <c r="I101">
+        <v>6910</v>
+      </c>
+      <c r="J101">
+        <v>195</v>
+      </c>
+      <c r="K101">
+        <v>3</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>3</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="R101" s="4">
+        <v>1.54E-2</v>
+      </c>
+      <c r="S101" s="5">
+        <v>0</v>
+      </c>
+      <c r="T101">
+        <v>0</v>
+      </c>
+      <c r="U101" s="5">
+        <v>0</v>
+      </c>
+      <c r="V101" s="4">
+        <v>1</v>
+      </c>
+      <c r="W101">
+        <v>42.584000000000003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B102">
+        <v>10</v>
+      </c>
+      <c r="C102">
+        <v>69</v>
+      </c>
+      <c r="D102">
+        <v>71</v>
+      </c>
+      <c r="E102" t="s">
+        <v>23</v>
+      </c>
+      <c r="F102">
+        <v>1637</v>
+      </c>
+      <c r="G102">
+        <v>7</v>
+      </c>
+      <c r="H102">
+        <v>3</v>
+      </c>
+      <c r="I102">
+        <v>6514</v>
+      </c>
+      <c r="J102">
+        <v>162</v>
+      </c>
+      <c r="K102">
+        <v>3</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P102" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="R102" s="4">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="S102" s="5">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>0</v>
+      </c>
+      <c r="U102" s="5">
+        <v>0</v>
+      </c>
+      <c r="V102" s="4">
+        <v>1</v>
+      </c>
+      <c r="W102">
+        <v>17.790500000000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B103">
+        <v>11</v>
+      </c>
+      <c r="C103">
+        <v>69</v>
+      </c>
+      <c r="D103">
+        <v>71</v>
+      </c>
+      <c r="E103" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103">
+        <v>1637</v>
+      </c>
+      <c r="G103">
+        <v>7</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>2275</v>
+      </c>
+      <c r="J103">
+        <v>78</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="P103" s="3">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="R103" s="4">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="S103" s="5">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>0</v>
+      </c>
+      <c r="U103" s="5">
+        <v>0</v>
+      </c>
+      <c r="V103" s="4">
+        <v>1</v>
+      </c>
+      <c r="W103">
+        <v>33.387</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B104">
+        <v>12</v>
+      </c>
+      <c r="C104">
+        <v>69</v>
+      </c>
+      <c r="D104">
+        <v>71</v>
+      </c>
+      <c r="E104" t="s">
+        <v>23</v>
+      </c>
+      <c r="F104">
+        <v>1637</v>
+      </c>
+      <c r="G104">
+        <v>7</v>
+      </c>
+      <c r="H104">
+        <v>2</v>
+      </c>
+      <c r="I104">
+        <v>4991</v>
+      </c>
+      <c r="J104">
+        <v>159</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>2</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="P104" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="R104" s="4">
+        <v>1.26E-2</v>
+      </c>
+      <c r="S104" s="5">
+        <v>0</v>
+      </c>
+      <c r="T104">
+        <v>0</v>
+      </c>
+      <c r="U104" s="5">
+        <v>0</v>
+      </c>
+      <c r="V104" s="4">
+        <v>1</v>
+      </c>
+      <c r="W104">
+        <v>36.835000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
+      <c r="C105">
+        <v>69</v>
+      </c>
+      <c r="D105">
+        <v>71</v>
+      </c>
+      <c r="E105" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105">
+        <v>1637</v>
+      </c>
+      <c r="G105">
+        <v>7</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>1942</v>
+      </c>
+      <c r="J105">
+        <v>48</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P105" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>2.47E-2</v>
+      </c>
+      <c r="R105" s="4">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="S105" s="5">
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105" s="5">
+        <v>0</v>
+      </c>
+      <c r="V105" s="4">
+        <v>1</v>
+      </c>
+      <c r="W105">
+        <v>9.3369999999999997</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B106">
+        <v>14</v>
+      </c>
+      <c r="C106">
+        <v>69</v>
+      </c>
+      <c r="D106">
+        <v>71</v>
+      </c>
+      <c r="E106" t="s">
+        <v>23</v>
+      </c>
+      <c r="F106">
+        <v>1637</v>
+      </c>
+      <c r="G106">
+        <v>7</v>
+      </c>
+      <c r="H106">
+        <v>2</v>
+      </c>
+      <c r="I106">
+        <v>4135</v>
+      </c>
+      <c r="J106">
+        <v>111</v>
+      </c>
+      <c r="K106">
+        <v>2</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>2</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P106" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="R106" s="4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="S106" s="5">
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <v>0</v>
+      </c>
+      <c r="U106" s="5">
+        <v>0</v>
+      </c>
+      <c r="V106" s="4">
+        <v>1</v>
+      </c>
+      <c r="W106">
+        <v>26.466000000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B107">
+        <v>15</v>
+      </c>
+      <c r="C107">
+        <v>69</v>
+      </c>
+      <c r="D107">
+        <v>71</v>
+      </c>
+      <c r="E107" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107">
+        <v>1637</v>
+      </c>
+      <c r="G107">
+        <v>7</v>
+      </c>
+      <c r="H107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>6193</v>
+      </c>
+      <c r="J107">
+        <v>140</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>2</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="P107" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="R107" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="S107" s="5">
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+      <c r="U107" s="5">
+        <v>0</v>
+      </c>
+      <c r="V107" s="4">
+        <v>1</v>
+      </c>
+      <c r="W107">
+        <v>39.051000000000002</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B108">
+        <v>16</v>
+      </c>
+      <c r="C108">
+        <v>69</v>
+      </c>
+      <c r="D108">
+        <v>71</v>
+      </c>
+      <c r="E108" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108">
+        <v>1637</v>
+      </c>
+      <c r="G108">
+        <v>7</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+      <c r="I108">
+        <v>1979</v>
+      </c>
+      <c r="J108">
+        <v>71</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>2</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="P108" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="Q108" s="4">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="R108" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="S108" s="5">
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <v>0</v>
+      </c>
+      <c r="U108" s="5">
+        <v>0</v>
+      </c>
+      <c r="V108" s="4">
+        <v>1</v>
+      </c>
+      <c r="W108">
+        <v>11.4015</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B109">
+        <v>17</v>
+      </c>
+      <c r="C109">
+        <v>69</v>
+      </c>
+      <c r="D109">
+        <v>71</v>
+      </c>
+      <c r="E109" t="s">
+        <v>23</v>
+      </c>
+      <c r="F109">
+        <v>1637</v>
+      </c>
+      <c r="G109">
+        <v>7</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>194</v>
+      </c>
+      <c r="J109">
+        <v>13</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="P109" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q109" s="4">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="R109" s="5">
+        <v>0</v>
+      </c>
+      <c r="S109" t="s">
+        <v>25</v>
+      </c>
+      <c r="T109">
+        <v>0</v>
+      </c>
+      <c r="U109" t="s">
+        <v>25</v>
+      </c>
+      <c r="V109" t="s">
+        <v>25</v>
+      </c>
+      <c r="W109">
+        <v>2.6379999999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B110">
+        <v>18</v>
+      </c>
+      <c r="C110">
+        <v>69</v>
+      </c>
+      <c r="D110">
+        <v>71</v>
+      </c>
+      <c r="E110" t="s">
+        <v>23</v>
+      </c>
+      <c r="F110">
+        <v>1637</v>
+      </c>
+      <c r="G110">
+        <v>7</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>1125</v>
+      </c>
+      <c r="J110">
+        <v>34</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P110" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="R110" s="4">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="S110" s="5">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110" s="5">
+        <v>0</v>
+      </c>
+      <c r="V110" s="4">
+        <v>1</v>
+      </c>
+      <c r="W110">
+        <v>6.9044999999999996</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B111">
+        <v>19</v>
+      </c>
+      <c r="C111">
+        <v>69</v>
+      </c>
+      <c r="D111">
+        <v>71</v>
+      </c>
+      <c r="E111" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111">
+        <v>1637</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>67</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111" t="s">
+        <v>24</v>
+      </c>
+      <c r="P111" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q111" s="5">
+        <v>0</v>
+      </c>
+      <c r="R111" t="s">
+        <v>25</v>
+      </c>
+      <c r="S111" t="s">
+        <v>25</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+      <c r="U111" t="s">
+        <v>25</v>
+      </c>
+      <c r="V111" t="s">
+        <v>25</v>
+      </c>
+      <c r="W111">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B112">
+        <v>8</v>
+      </c>
+      <c r="C112">
+        <v>69</v>
+      </c>
+      <c r="D112">
+        <v>71</v>
+      </c>
+      <c r="E112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112">
+        <v>1973</v>
+      </c>
+      <c r="G112">
+        <v>7</v>
+      </c>
+      <c r="H112">
+        <v>3</v>
+      </c>
+      <c r="I112">
+        <v>7408</v>
+      </c>
+      <c r="J112">
+        <v>170</v>
+      </c>
+      <c r="K112">
+        <v>3</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>3</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P112" s="3">
+        <v>1.8055555555555555E-3</v>
+      </c>
+      <c r="Q112" s="4">
+        <v>2.29E-2</v>
+      </c>
+      <c r="R112" s="4">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="S112" s="5">
+        <v>0</v>
+      </c>
+      <c r="T112">
+        <v>0</v>
+      </c>
+      <c r="U112" s="5">
+        <v>0</v>
+      </c>
+      <c r="V112" s="4">
+        <v>1</v>
+      </c>
+      <c r="W112">
+        <v>73.662000000000006</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B113">
+        <v>9</v>
+      </c>
+      <c r="C113">
+        <v>69</v>
+      </c>
+      <c r="D113">
+        <v>71</v>
+      </c>
+      <c r="E113" t="s">
+        <v>23</v>
+      </c>
+      <c r="F113">
+        <v>1973</v>
+      </c>
+      <c r="G113">
+        <v>7</v>
+      </c>
+      <c r="H113">
+        <v>8</v>
+      </c>
+      <c r="I113">
+        <v>7448</v>
+      </c>
+      <c r="J113">
+        <v>248</v>
+      </c>
+      <c r="K113">
+        <v>11</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>10</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="P113" s="3">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="Q113" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="R113" s="4">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="S113" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="T113">
+        <v>0</v>
+      </c>
+      <c r="U113" s="5">
+        <v>0</v>
+      </c>
+      <c r="V113" s="4">
+        <v>1</v>
+      </c>
+      <c r="W113">
+        <v>40.516500000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B114">
+        <v>10</v>
+      </c>
+      <c r="C114">
+        <v>69</v>
+      </c>
+      <c r="D114">
+        <v>71</v>
+      </c>
+      <c r="E114" t="s">
+        <v>23</v>
+      </c>
+      <c r="F114">
+        <v>1973</v>
+      </c>
+      <c r="G114">
+        <v>7</v>
+      </c>
+      <c r="H114">
+        <v>2</v>
+      </c>
+      <c r="I114">
+        <v>5002</v>
+      </c>
+      <c r="J114">
+        <v>178</v>
+      </c>
+      <c r="K114">
+        <v>3</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="P114" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>3.56E-2</v>
+      </c>
+      <c r="R114" s="4">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="S114" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="T114">
+        <v>0</v>
+      </c>
+      <c r="U114" s="5">
+        <v>0</v>
+      </c>
+      <c r="V114" s="4">
+        <v>1</v>
+      </c>
+      <c r="W114">
+        <v>17.309999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B115">
+        <v>11</v>
+      </c>
+      <c r="C115">
+        <v>69</v>
+      </c>
+      <c r="D115">
+        <v>71</v>
+      </c>
+      <c r="E115" t="s">
+        <v>23</v>
+      </c>
+      <c r="F115">
+        <v>1973</v>
+      </c>
+      <c r="G115">
+        <v>7</v>
+      </c>
+      <c r="H115">
+        <v>5</v>
+      </c>
+      <c r="I115">
+        <v>6926</v>
+      </c>
+      <c r="J115">
+        <v>302</v>
+      </c>
+      <c r="K115">
+        <v>6</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>6</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="P115" s="3">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="Q115" s="4">
+        <v>4.36E-2</v>
+      </c>
+      <c r="R115" s="4">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="S115" s="5">
+        <v>0</v>
+      </c>
+      <c r="T115">
+        <v>0</v>
+      </c>
+      <c r="U115" s="5">
+        <v>0</v>
+      </c>
+      <c r="V115" s="4">
+        <v>1</v>
+      </c>
+      <c r="W115">
+        <v>58.563499999999998</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B116">
+        <v>12</v>
+      </c>
+      <c r="C116">
+        <v>69</v>
+      </c>
+      <c r="D116">
+        <v>71</v>
+      </c>
+      <c r="E116" t="s">
+        <v>23</v>
+      </c>
+      <c r="F116">
+        <v>1973</v>
+      </c>
+      <c r="G116">
+        <v>7</v>
+      </c>
+      <c r="H116">
+        <v>6</v>
+      </c>
+      <c r="I116">
+        <v>3146</v>
+      </c>
+      <c r="J116">
+        <v>134</v>
+      </c>
+      <c r="K116">
+        <v>6</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>6</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P116" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="Q116" s="4">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="R116" s="4">
+        <v>4.48E-2</v>
+      </c>
+      <c r="S116" s="5">
+        <v>0</v>
+      </c>
+      <c r="T116">
+        <v>0</v>
+      </c>
+      <c r="U116" s="5">
+        <v>0</v>
+      </c>
+      <c r="V116" s="4">
+        <v>1</v>
+      </c>
+      <c r="W116">
+        <v>24.705500000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B117">
+        <v>13</v>
+      </c>
+      <c r="C117">
+        <v>69</v>
+      </c>
+      <c r="D117">
+        <v>71</v>
+      </c>
+      <c r="E117" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117">
+        <v>1973</v>
+      </c>
+      <c r="G117">
+        <v>7</v>
+      </c>
+      <c r="H117">
+        <v>3</v>
+      </c>
+      <c r="I117">
+        <v>2442</v>
+      </c>
+      <c r="J117">
+        <v>75</v>
+      </c>
+      <c r="K117">
+        <v>3</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>3</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="P117" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="Q117" s="4">
+        <v>3.0700000000000002E-2</v>
+      </c>
+      <c r="R117" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="S117" s="5">
+        <v>0</v>
+      </c>
+      <c r="T117">
+        <v>0</v>
+      </c>
+      <c r="U117" s="5">
+        <v>0</v>
+      </c>
+      <c r="V117" s="4">
+        <v>1</v>
+      </c>
+      <c r="W117">
+        <v>12.333</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B118">
+        <v>14</v>
+      </c>
+      <c r="C118">
+        <v>69</v>
+      </c>
+      <c r="D118">
+        <v>71</v>
+      </c>
+      <c r="E118" t="s">
+        <v>23</v>
+      </c>
+      <c r="F118">
+        <v>1973</v>
+      </c>
+      <c r="G118">
+        <v>7</v>
+      </c>
+      <c r="H118">
+        <v>6</v>
+      </c>
+      <c r="I118">
+        <v>6093</v>
+      </c>
+      <c r="J118">
+        <v>230</v>
+      </c>
+      <c r="K118">
+        <v>7</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>7</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="P118" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="Q118" s="4">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R118" s="4">
+        <v>3.04E-2</v>
+      </c>
+      <c r="S118" s="5">
+        <v>0</v>
+      </c>
+      <c r="T118">
+        <v>0</v>
+      </c>
+      <c r="U118" s="5">
+        <v>0</v>
+      </c>
+      <c r="V118" s="4">
+        <v>1</v>
+      </c>
+      <c r="W118">
+        <v>49.092500000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B119">
+        <v>15</v>
+      </c>
+      <c r="C119">
+        <v>69</v>
+      </c>
+      <c r="D119">
+        <v>71</v>
+      </c>
+      <c r="E119" t="s">
+        <v>23</v>
+      </c>
+      <c r="F119">
+        <v>1973</v>
+      </c>
+      <c r="G119">
+        <v>7</v>
+      </c>
+      <c r="H119">
+        <v>5</v>
+      </c>
+      <c r="I119">
+        <v>3902</v>
+      </c>
+      <c r="J119">
+        <v>249</v>
+      </c>
+      <c r="K119">
+        <v>5</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>5</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P119" s="3">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="Q119" s="4">
+        <v>6.3799999999999996E-2</v>
+      </c>
+      <c r="R119" s="4">
+        <v>2.01E-2</v>
+      </c>
+      <c r="S119" s="5">
+        <v>0</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" s="5">
+        <v>0</v>
+      </c>
+      <c r="V119" s="4">
+        <v>1</v>
+      </c>
+      <c r="W119">
+        <v>39.319000000000003</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B120">
+        <v>16</v>
+      </c>
+      <c r="C120">
+        <v>69</v>
+      </c>
+      <c r="D120">
+        <v>71</v>
+      </c>
+      <c r="E120" t="s">
+        <v>23</v>
+      </c>
+      <c r="F120">
+        <v>1973</v>
+      </c>
+      <c r="G120">
+        <v>7</v>
+      </c>
+      <c r="H120">
+        <v>3</v>
+      </c>
+      <c r="I120">
+        <v>4844</v>
+      </c>
+      <c r="J120">
+        <v>283</v>
+      </c>
+      <c r="K120">
+        <v>3</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>3</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="P120" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>5.8400000000000001E-2</v>
+      </c>
+      <c r="R120" s="4">
+        <v>1.06E-2</v>
+      </c>
+      <c r="S120" s="5">
+        <v>0</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120" s="5">
+        <v>0</v>
+      </c>
+      <c r="V120" s="4">
+        <v>1</v>
+      </c>
+      <c r="W120">
+        <v>28.517499999999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B121">
+        <v>17</v>
+      </c>
+      <c r="C121">
+        <v>69</v>
+      </c>
+      <c r="D121">
+        <v>71</v>
+      </c>
+      <c r="E121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121">
+        <v>1973</v>
+      </c>
+      <c r="G121">
+        <v>7</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>4188</v>
+      </c>
+      <c r="J121">
+        <v>112</v>
+      </c>
+      <c r="K121">
+        <v>2</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P121" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="R121" s="4">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="S121" s="5">
+        <v>1</v>
+      </c>
+      <c r="T121">
+        <v>0</v>
+      </c>
+      <c r="U121" t="s">
+        <v>25</v>
+      </c>
+      <c r="V121" t="s">
+        <v>25</v>
+      </c>
+      <c r="W121">
+        <v>16.1815</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B122">
+        <v>18</v>
+      </c>
+      <c r="C122">
+        <v>69</v>
+      </c>
+      <c r="D122">
+        <v>71</v>
+      </c>
+      <c r="E122" t="s">
+        <v>23</v>
+      </c>
+      <c r="F122">
+        <v>1973</v>
+      </c>
+      <c r="G122">
+        <v>7</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>623</v>
+      </c>
+      <c r="J122">
+        <v>30</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P122" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>4.82E-2</v>
+      </c>
+      <c r="R122" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="S122" s="5">
+        <v>1</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122" t="s">
+        <v>25</v>
+      </c>
+      <c r="V122" t="s">
+        <v>25</v>
+      </c>
+      <c r="W122">
+        <v>3.4060000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B123">
+        <v>19</v>
+      </c>
+      <c r="C123">
+        <v>69</v>
+      </c>
+      <c r="D123">
+        <v>71</v>
+      </c>
+      <c r="E123" t="s">
+        <v>23</v>
+      </c>
+      <c r="F123">
+        <v>1973</v>
+      </c>
+      <c r="G123">
+        <v>7</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>952</v>
+      </c>
+      <c r="J123">
+        <v>18</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P123" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q123" s="4">
+        <v>1.89E-2</v>
+      </c>
+      <c r="R123" s="5">
+        <v>0</v>
+      </c>
+      <c r="S123" t="s">
+        <v>25</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+      <c r="U123" t="s">
+        <v>25</v>
+      </c>
+      <c r="V123" t="s">
+        <v>25</v>
+      </c>
+      <c r="W123">
+        <v>4.5694999999999997</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B124">
+        <v>8</v>
+      </c>
+      <c r="C124">
+        <v>69</v>
+      </c>
+      <c r="D124">
+        <v>71</v>
+      </c>
+      <c r="E124" t="s">
+        <v>23</v>
+      </c>
+      <c r="F124">
+        <v>1829</v>
+      </c>
+      <c r="G124">
+        <v>7</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>1024</v>
+      </c>
+      <c r="J124">
+        <v>23</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P124" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="R124" s="5">
+        <v>0</v>
+      </c>
+      <c r="S124" t="s">
+        <v>25</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124" t="s">
+        <v>25</v>
+      </c>
+      <c r="V124" t="s">
+        <v>25</v>
+      </c>
+      <c r="W124">
+        <v>5.7255000000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B125">
+        <v>9</v>
+      </c>
+      <c r="C125">
+        <v>69</v>
+      </c>
+      <c r="D125">
+        <v>71</v>
+      </c>
+      <c r="E125" t="s">
+        <v>23</v>
+      </c>
+      <c r="F125">
+        <v>1829</v>
+      </c>
+      <c r="G125">
+        <v>7</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+      <c r="I125">
+        <v>2440</v>
+      </c>
+      <c r="J125">
+        <v>35</v>
+      </c>
+      <c r="K125">
+        <v>2</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>2</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125" s="3">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="P125" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="Q125" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="R125" s="4">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="S125" s="5">
+        <v>0</v>
+      </c>
+      <c r="T125">
+        <v>0</v>
+      </c>
+      <c r="U125" s="5">
+        <v>0</v>
+      </c>
+      <c r="V125" s="4">
+        <v>1</v>
+      </c>
+      <c r="W125">
+        <v>24.28</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B126">
+        <v>10</v>
+      </c>
+      <c r="C126">
+        <v>69</v>
+      </c>
+      <c r="D126">
+        <v>71</v>
+      </c>
+      <c r="E126" t="s">
+        <v>23</v>
+      </c>
+      <c r="F126">
+        <v>1829</v>
+      </c>
+      <c r="G126">
+        <v>7</v>
+      </c>
+      <c r="H126">
+        <v>5</v>
+      </c>
+      <c r="I126">
+        <v>4637</v>
+      </c>
+      <c r="J126">
+        <v>107</v>
+      </c>
+      <c r="K126">
+        <v>7</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>7</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P126" s="3">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="R126" s="4">
+        <v>6.54E-2</v>
+      </c>
+      <c r="S126" s="5">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126" s="5">
+        <v>0</v>
+      </c>
+      <c r="V126" s="4">
+        <v>1</v>
+      </c>
+      <c r="W126">
+        <v>46.672499999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B127">
+        <v>11</v>
+      </c>
+      <c r="C127">
+        <v>69</v>
+      </c>
+      <c r="D127">
+        <v>71</v>
+      </c>
+      <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127">
+        <v>1829</v>
+      </c>
+      <c r="G127">
+        <v>7</v>
+      </c>
+      <c r="H127">
+        <v>2</v>
+      </c>
+      <c r="I127">
+        <v>1118</v>
+      </c>
+      <c r="J127">
+        <v>15</v>
+      </c>
+      <c r="K127">
+        <v>2</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>2</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="P127" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>1.34E-2</v>
+      </c>
+      <c r="R127" s="4">
+        <v>0.1333</v>
+      </c>
+      <c r="S127" s="5">
+        <v>0</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127" s="5">
+        <v>0</v>
+      </c>
+      <c r="V127" s="4">
+        <v>1</v>
+      </c>
+      <c r="W127">
+        <v>4.2320000000000002</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B128">
+        <v>12</v>
+      </c>
+      <c r="C128">
+        <v>69</v>
+      </c>
+      <c r="D128">
+        <v>71</v>
+      </c>
+      <c r="E128" t="s">
+        <v>23</v>
+      </c>
+      <c r="F128">
+        <v>1829</v>
+      </c>
+      <c r="G128">
+        <v>7</v>
+      </c>
+      <c r="H128">
+        <v>2</v>
+      </c>
+      <c r="I128">
+        <v>2990</v>
+      </c>
+      <c r="J128">
+        <v>46</v>
+      </c>
+      <c r="K128">
+        <v>2</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>2</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="P128" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>1.54E-2</v>
+      </c>
+      <c r="R128" s="4">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="S128" s="5">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128" s="5">
+        <v>0</v>
+      </c>
+      <c r="V128" s="4">
+        <v>1</v>
+      </c>
+      <c r="W128">
+        <v>25.16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B129">
+        <v>13</v>
+      </c>
+      <c r="C129">
+        <v>69</v>
+      </c>
+      <c r="D129">
+        <v>71</v>
+      </c>
+      <c r="E129" t="s">
+        <v>23</v>
+      </c>
+      <c r="F129">
+        <v>1829</v>
+      </c>
+      <c r="G129">
+        <v>7</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>2086</v>
+      </c>
+      <c r="J129">
+        <v>69</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="P129" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="R129" s="4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S129" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+      <c r="U129" s="5">
+        <v>0</v>
+      </c>
+      <c r="V129" s="4">
+        <v>1</v>
+      </c>
+      <c r="W129">
+        <v>39.118000000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B130">
+        <v>14</v>
+      </c>
+      <c r="C130">
+        <v>69</v>
+      </c>
+      <c r="D130">
+        <v>71</v>
+      </c>
+      <c r="E130" t="s">
+        <v>23</v>
+      </c>
+      <c r="F130">
+        <v>1829</v>
+      </c>
+      <c r="G130">
+        <v>7</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>2428</v>
+      </c>
+      <c r="J130">
+        <v>38</v>
+      </c>
+      <c r="K130">
+        <v>2</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P130" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q130" s="4">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="R130" s="4">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="S130" s="5">
+        <v>1</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130" t="s">
+        <v>25</v>
+      </c>
+      <c r="V130" t="s">
+        <v>25</v>
+      </c>
+      <c r="W130">
+        <v>9.0664999999999996</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B131">
+        <v>15</v>
+      </c>
+      <c r="C131">
+        <v>69</v>
+      </c>
+      <c r="D131">
+        <v>71</v>
+      </c>
+      <c r="E131" t="s">
+        <v>23</v>
+      </c>
+      <c r="F131">
+        <v>1829</v>
+      </c>
+      <c r="G131">
+        <v>7</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>1145</v>
+      </c>
+      <c r="J131">
+        <v>41</v>
+      </c>
+      <c r="K131">
+        <v>4</v>
+      </c>
+      <c r="L131">
+        <v>4</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="P131" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q131" s="4">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="R131" s="4">
+        <v>9.7600000000000006E-2</v>
+      </c>
+      <c r="S131" s="5">
+        <v>1</v>
+      </c>
+      <c r="T131">
+        <v>0</v>
+      </c>
+      <c r="U131" t="s">
+        <v>25</v>
+      </c>
+      <c r="V131" t="s">
+        <v>25</v>
+      </c>
+      <c r="W131">
+        <v>19.808499999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B132">
+        <v>8</v>
+      </c>
+      <c r="C132">
+        <v>69</v>
+      </c>
+      <c r="D132">
+        <v>71</v>
+      </c>
+      <c r="E132" t="s">
+        <v>23</v>
+      </c>
+      <c r="F132">
+        <v>2687</v>
+      </c>
+      <c r="G132">
+        <v>7</v>
+      </c>
+      <c r="H132">
+        <v>5</v>
+      </c>
+      <c r="I132">
+        <v>7030</v>
+      </c>
+      <c r="J132">
+        <v>160</v>
+      </c>
+      <c r="K132">
+        <v>6</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>6</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="P132" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="Q132" s="4">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="R132" s="4">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="S132" s="5">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132" s="5">
+        <v>0</v>
+      </c>
+      <c r="V132" s="4">
+        <v>1</v>
+      </c>
+      <c r="W132">
+        <v>69.533500000000004</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B133">
+        <v>9</v>
+      </c>
+      <c r="C133">
+        <v>69</v>
+      </c>
+      <c r="D133">
+        <v>71</v>
+      </c>
+      <c r="E133" t="s">
+        <v>23</v>
+      </c>
+      <c r="F133">
+        <v>2687</v>
+      </c>
+      <c r="G133">
+        <v>7</v>
+      </c>
+      <c r="H133">
+        <v>5</v>
+      </c>
+      <c r="I133">
+        <v>5804</v>
+      </c>
+      <c r="J133">
+        <v>180</v>
+      </c>
+      <c r="K133">
+        <v>5</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>5</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="P133" s="3">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q133" s="4">
+        <v>3.1E-2</v>
+      </c>
+      <c r="R133" s="4">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="S133" s="5">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133" s="5">
+        <v>0</v>
+      </c>
+      <c r="V133" s="4">
+        <v>1</v>
+      </c>
+      <c r="W133">
+        <v>35.280999999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B134">
+        <v>10</v>
+      </c>
+      <c r="C134">
+        <v>69</v>
+      </c>
+      <c r="D134">
+        <v>71</v>
+      </c>
+      <c r="E134" t="s">
+        <v>23</v>
+      </c>
+      <c r="F134">
+        <v>2687</v>
+      </c>
+      <c r="G134">
+        <v>7</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>572</v>
+      </c>
+      <c r="J134">
+        <v>22</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P134" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q134" s="4">
+        <v>3.85E-2</v>
+      </c>
+      <c r="R134" s="4">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="S134" s="5">
+        <v>1</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134" t="s">
+        <v>25</v>
+      </c>
+      <c r="V134" t="s">
+        <v>25</v>
+      </c>
+      <c r="W134">
+        <v>2.9125000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B135">
+        <v>11</v>
+      </c>
+      <c r="C135">
+        <v>69</v>
+      </c>
+      <c r="D135">
+        <v>71</v>
+      </c>
+      <c r="E135" t="s">
+        <v>23</v>
+      </c>
+      <c r="F135">
+        <v>2687</v>
+      </c>
+      <c r="G135">
+        <v>7</v>
+      </c>
+      <c r="H135">
+        <v>2</v>
+      </c>
+      <c r="I135">
+        <v>8339</v>
+      </c>
+      <c r="J135">
+        <v>204</v>
+      </c>
+      <c r="K135">
+        <v>3</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>2</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P135" s="3">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="Q135" s="4">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="R135" s="4">
+        <v>1.47E-2</v>
+      </c>
+      <c r="S135" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135" s="5">
+        <v>0</v>
+      </c>
+      <c r="V135" s="4">
+        <v>1</v>
+      </c>
+      <c r="W135">
+        <v>63.496000000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B136">
+        <v>12</v>
+      </c>
+      <c r="C136">
+        <v>69</v>
+      </c>
+      <c r="D136">
+        <v>71</v>
+      </c>
+      <c r="E136" t="s">
+        <v>23</v>
+      </c>
+      <c r="F136">
+        <v>2687</v>
+      </c>
+      <c r="G136">
+        <v>7</v>
+      </c>
+      <c r="H136">
+        <v>2</v>
+      </c>
+      <c r="I136">
+        <v>3800</v>
+      </c>
+      <c r="J136">
+        <v>107</v>
+      </c>
+      <c r="K136">
+        <v>2</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>2</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P136" s="3">
+        <v>3.7499999999999999E-3</v>
+      </c>
+      <c r="Q136" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="R136" s="4">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="S136" s="5">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136" s="5">
+        <v>0</v>
+      </c>
+      <c r="V136" s="4">
+        <v>1</v>
+      </c>
+      <c r="W136">
+        <v>26.101500000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B137">
+        <v>13</v>
+      </c>
+      <c r="C137">
+        <v>69</v>
+      </c>
+      <c r="D137">
+        <v>71</v>
+      </c>
+      <c r="E137" t="s">
+        <v>23</v>
+      </c>
+      <c r="F137">
+        <v>2687</v>
+      </c>
+      <c r="G137">
+        <v>7</v>
+      </c>
+      <c r="H137">
+        <v>8</v>
+      </c>
+      <c r="I137">
+        <v>5568</v>
+      </c>
+      <c r="J137">
+        <v>147</v>
+      </c>
+      <c r="K137">
+        <v>8</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>8</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="P137" s="3">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="Q137" s="4">
+        <v>2.64E-2</v>
+      </c>
+      <c r="R137" s="4">
+        <v>5.4399999999999997E-2</v>
+      </c>
+      <c r="S137" s="5">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137" s="5">
+        <v>0</v>
+      </c>
+      <c r="V137" s="4">
+        <v>1</v>
+      </c>
+      <c r="W137">
+        <v>43.073</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A138" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B138">
+        <v>14</v>
+      </c>
+      <c r="C138">
+        <v>69</v>
+      </c>
+      <c r="D138">
+        <v>71</v>
+      </c>
+      <c r="E138" t="s">
+        <v>23</v>
+      </c>
+      <c r="F138">
+        <v>2687</v>
+      </c>
+      <c r="G138">
+        <v>7</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>1818</v>
+      </c>
+      <c r="J138">
+        <v>44</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P138" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q138" s="4">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="R138" s="5">
+        <v>0</v>
+      </c>
+      <c r="S138" t="s">
+        <v>25</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138" t="s">
+        <v>25</v>
+      </c>
+      <c r="V138" t="s">
+        <v>25</v>
+      </c>
+      <c r="W138">
+        <v>9.6385000000000005</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A139" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B139">
+        <v>15</v>
+      </c>
+      <c r="C139">
+        <v>69</v>
+      </c>
+      <c r="D139">
+        <v>71</v>
+      </c>
+      <c r="E139" t="s">
+        <v>23</v>
+      </c>
+      <c r="F139">
+        <v>2687</v>
+      </c>
+      <c r="G139">
+        <v>7</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>2982</v>
+      </c>
+      <c r="J139">
+        <v>51</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="P139" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q139" s="4">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="R139" s="5">
+        <v>0</v>
+      </c>
+      <c r="S139" t="s">
+        <v>25</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139" t="s">
+        <v>25</v>
+      </c>
+      <c r="V139" t="s">
+        <v>25</v>
+      </c>
+      <c r="W139">
+        <v>8.0175000000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B140">
+        <v>16</v>
+      </c>
+      <c r="C140">
+        <v>69</v>
+      </c>
+      <c r="D140">
+        <v>71</v>
+      </c>
+      <c r="E140" t="s">
+        <v>23</v>
+      </c>
+      <c r="F140">
+        <v>2687</v>
+      </c>
+      <c r="G140">
+        <v>7</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>4854</v>
+      </c>
+      <c r="J140">
+        <v>76</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P140" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="Q140" s="4">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="R140" s="4">
+        <v>1.32E-2</v>
+      </c>
+      <c r="S140" s="5">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140" s="5">
+        <v>0</v>
+      </c>
+      <c r="V140" s="4">
+        <v>1</v>
+      </c>
+      <c r="W140">
+        <v>25.107500000000002</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A141" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B141">
+        <v>17</v>
+      </c>
+      <c r="C141">
+        <v>69</v>
+      </c>
+      <c r="D141">
+        <v>71</v>
+      </c>
+      <c r="E141" t="s">
+        <v>23</v>
+      </c>
+      <c r="F141">
+        <v>2687</v>
+      </c>
+      <c r="G141">
+        <v>7</v>
+      </c>
+      <c r="H141">
+        <v>2</v>
+      </c>
+      <c r="I141">
+        <v>1399</v>
+      </c>
+      <c r="J141">
+        <v>27</v>
+      </c>
+      <c r="K141">
+        <v>2</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>2</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="P141" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="Q141" s="4">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="R141" s="4">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="S141" s="5">
+        <v>0</v>
+      </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+      <c r="U141" s="5">
+        <v>0</v>
+      </c>
+      <c r="V141" s="4">
+        <v>1</v>
+      </c>
+      <c r="W141">
+        <v>9.4184999999999999</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B142">
+        <v>18</v>
+      </c>
+      <c r="C142">
+        <v>69</v>
+      </c>
+      <c r="D142">
+        <v>71</v>
+      </c>
+      <c r="E142" t="s">
+        <v>23</v>
+      </c>
+      <c r="F142">
+        <v>2687</v>
+      </c>
+      <c r="G142">
+        <v>7</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>214</v>
+      </c>
+      <c r="J142">
+        <v>11</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P142" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q142" s="4">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="R142" s="5">
+        <v>0</v>
+      </c>
+      <c r="S142" t="s">
+        <v>25</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="U142" t="s">
+        <v>25</v>
+      </c>
+      <c r="V142" t="s">
+        <v>25</v>
+      </c>
+      <c r="W142">
+        <v>3.1435</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A143" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B143">
+        <v>19</v>
+      </c>
+      <c r="C143">
+        <v>69</v>
+      </c>
+      <c r="D143">
+        <v>71</v>
+      </c>
+      <c r="E143" t="s">
+        <v>23</v>
+      </c>
+      <c r="F143">
+        <v>2687</v>
+      </c>
+      <c r="G143">
+        <v>7</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>1602</v>
+      </c>
+      <c r="J143">
+        <v>17</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143" s="3">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="P143" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q143" s="4">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R143" s="5">
+        <v>0</v>
+      </c>
+      <c r="S143" t="s">
+        <v>25</v>
+      </c>
+      <c r="T143">
+        <v>0</v>
+      </c>
+      <c r="U143" t="s">
+        <v>25</v>
+      </c>
+      <c r="V143" t="s">
+        <v>25</v>
+      </c>
+      <c r="W143">
+        <v>17.626999999999999</v>
       </c>
     </row>
   </sheetData>
